--- a/curriculum.xlsx
+++ b/curriculum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CDA9F6-9430-4299-B84B-2D05ECE8797E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D0550F-C7B9-43C7-B73A-314EDEFC6733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maths" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="733">
   <si>
     <t>Concept</t>
   </si>
@@ -105,9 +105,6 @@
     <t xml:space="preserve">    • Complex conjugate: z* = a - bi; Modulus (magnitude): |z| = √(a² + b²) = √(z · z*)</t>
   </si>
   <si>
-    <t xml:space="preserve">    • Argument (phase angle): arg(z) = θ = atan2(b, a)</t>
-  </si>
-  <si>
     <t xml:space="preserve">    • Euler's Formula: e^(iθ) = cos(θ) + i sin(θ)</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
   </si>
   <si>
     <t xml:space="preserve">    • L'Hôpital's Rule for indeterminate forms (0/0, ∞/∞)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    • Asymptotic notation: Big-O O(f(n)) and little-o o(f(n))</t>
   </si>
   <si>
     <t>2.2 Differential Calculus (Derivatives)</t>
@@ -2233,7 +2227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2269,6 +2263,23 @@
       <color rgb="FF222222"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF111111"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2297,13 +2308,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor rgb="FFF2F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2335,7 +2346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2361,7 +2372,24 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2666,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="115" customWidth="1"/>
@@ -2681,245 +2709,245 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="B4" s="12"/>
+    </row>
+    <row r="5" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="12"/>
+    </row>
+    <row r="6" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="12"/>
+    </row>
+    <row r="7" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="B8" s="6"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="B7" s="9"/>
+    </row>
+    <row r="8" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="B8" s="12"/>
+    </row>
+    <row r="9" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="12"/>
+    </row>
+    <row r="10" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="12"/>
+    </row>
+    <row r="12" spans="1:2" s="15" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="14"/>
+    </row>
+    <row r="13" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="B13" s="12"/>
+    </row>
+    <row r="14" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="12"/>
+    </row>
+    <row r="15" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="12"/>
+    </row>
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="B17" s="12"/>
+    </row>
+    <row r="18" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="6"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="6"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+      <c r="B22" s="12"/>
+    </row>
+    <row r="23" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="12"/>
+    </row>
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="B25" s="12"/>
+    </row>
+    <row r="26" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="6"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+      <c r="B26" s="12"/>
+    </row>
+    <row r="27" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="6"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="12"/>
+    </row>
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="6"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="6"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="6"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="6"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="B33" s="9"/>
+    </row>
+    <row r="34" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="5" t="s">
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="B35" s="12"/>
+    </row>
+    <row r="36" spans="1:2" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="6"/>
+      <c r="B36" s="12"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="6"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="6"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+      <c r="B38" s="12"/>
+    </row>
+    <row r="39" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
+      <c r="B39" s="12"/>
+    </row>
+    <row r="40" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="6"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="B40" s="12"/>
+    </row>
+    <row r="41" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6"/>
+      <c r="B41" s="12"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
@@ -2946,10 +2974,10 @@
       <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="6"/>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
@@ -2958,10 +2986,10 @@
       <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="4"/>
+      <c r="B48" s="6"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
@@ -2988,10 +3016,10 @@
       <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="6"/>
+      <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
@@ -3000,10 +3028,10 @@
       <c r="B54" s="6"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="4"/>
+      <c r="B55" s="6"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
@@ -3036,28 +3064,28 @@
       <c r="B60" s="6"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="6"/>
+      <c r="B61" s="2"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="6"/>
+      <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2"/>
+      <c r="B63" s="6"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="4"/>
+      <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
@@ -3084,10 +3112,10 @@
       <c r="B68" s="6"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="6"/>
+      <c r="B69" s="4"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
@@ -3096,10 +3124,10 @@
       <c r="B70" s="6"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="4"/>
+      <c r="B71" s="6"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
@@ -3138,10 +3166,10 @@
       <c r="B77" s="6"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="6"/>
+      <c r="B78" s="4"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
@@ -3150,10 +3178,10 @@
       <c r="B79" s="6"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="4"/>
+      <c r="B80" s="6"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
@@ -3168,10 +3196,10 @@
       <c r="B82" s="6"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="6"/>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
@@ -3180,10 +3208,10 @@
       <c r="B84" s="6"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="4"/>
+      <c r="B85" s="6"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
@@ -3192,10 +3220,10 @@
       <c r="B86" s="6"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="6"/>
+      <c r="B87" s="4"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
@@ -3204,10 +3232,10 @@
       <c r="B88" s="6"/>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="4"/>
+      <c r="B89" s="6"/>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
@@ -3246,28 +3274,28 @@
       <c r="B95" s="6"/>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="6"/>
+      <c r="B96" s="2"/>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="6"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2"/>
+      <c r="B98" s="6"/>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="4"/>
+      <c r="B99" s="6"/>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
@@ -3318,10 +3346,10 @@
       <c r="B107" s="6"/>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="6"/>
+      <c r="B108" s="4"/>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
@@ -3330,10 +3358,10 @@
       <c r="B109" s="6"/>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="4"/>
+      <c r="B110" s="6"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
@@ -3378,10 +3406,10 @@
       <c r="B117" s="6"/>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="6"/>
+      <c r="B118" s="4"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
@@ -3390,10 +3418,10 @@
       <c r="B119" s="6"/>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="4"/>
+      <c r="B120" s="6"/>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
@@ -3402,13 +3430,13 @@
       <c r="B121" s="6"/>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B122" s="6"/>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="5" t="s">
+      <c r="A123" s="7" t="s">
         <v>122</v>
       </c>
       <c r="B123" s="6"/>
@@ -3426,13 +3454,13 @@
       <c r="B125" s="6"/>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B126" s="6"/>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B127" s="6"/>
@@ -3444,10 +3472,10 @@
       <c r="B128" s="6"/>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="6"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
@@ -3456,10 +3484,10 @@
       <c r="B130" s="6"/>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B131" s="4"/>
+      <c r="B131" s="6"/>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
@@ -3492,10 +3520,10 @@
       <c r="B136" s="6"/>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="6"/>
+      <c r="B137" s="4"/>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
@@ -3504,10 +3532,10 @@
       <c r="B138" s="6"/>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B139" s="4"/>
+      <c r="B139" s="6"/>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
@@ -3521,7 +3549,7 @@
       </c>
       <c r="B141" s="6"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>141</v>
       </c>
@@ -3533,7 +3561,7 @@
       </c>
       <c r="B143" s="6"/>
     </row>
-    <row r="144" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>143</v>
       </c>
@@ -3558,28 +3586,28 @@
       <c r="B147" s="6"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B148" s="6"/>
+      <c r="B148" s="2"/>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" s="5" t="s">
+      <c r="A149" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="6"/>
+      <c r="B149" s="4"/>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B150" s="2"/>
+      <c r="B150" s="6"/>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" s="3" t="s">
+      <c r="A151" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B151" s="4"/>
+      <c r="B151" s="6"/>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
@@ -3606,10 +3634,10 @@
       <c r="B155" s="6"/>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B156" s="6"/>
+      <c r="B156" s="4"/>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
@@ -3618,10 +3646,10 @@
       <c r="B157" s="6"/>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="3" t="s">
+      <c r="A158" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B158" s="4"/>
+      <c r="B158" s="6"/>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
@@ -3648,10 +3676,10 @@
       <c r="B162" s="6"/>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B163" s="6"/>
+      <c r="B163" s="4"/>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
@@ -3660,10 +3688,10 @@
       <c r="B164" s="6"/>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B165" s="4"/>
+      <c r="B165" s="6"/>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
@@ -3702,10 +3730,10 @@
       <c r="B171" s="6"/>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A172" s="5" t="s">
+      <c r="A172" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B172" s="6"/>
+      <c r="B172" s="4"/>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
@@ -3714,10 +3742,10 @@
       <c r="B173" s="6"/>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A174" s="3" t="s">
+      <c r="A174" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B174" s="4"/>
+      <c r="B174" s="6"/>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
@@ -3744,10 +3772,10 @@
       <c r="B178" s="6"/>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A179" s="5" t="s">
+      <c r="A179" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B179" s="6"/>
+      <c r="B179" s="4"/>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
@@ -3756,10 +3784,10 @@
       <c r="B180" s="6"/>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B181" s="4"/>
+      <c r="B181" s="6"/>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
@@ -3774,10 +3802,10 @@
       <c r="B183" s="6"/>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B184" s="6"/>
+      <c r="B184" s="4"/>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
@@ -3786,10 +3814,10 @@
       <c r="B185" s="6"/>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A186" s="3" t="s">
+      <c r="A186" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B186" s="4"/>
+      <c r="B186" s="6"/>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
@@ -3816,10 +3844,10 @@
       <c r="B190" s="6"/>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A191" s="5" t="s">
+      <c r="A191" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B191" s="6"/>
+      <c r="B191" s="4"/>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
@@ -3828,10 +3856,10 @@
       <c r="B192" s="6"/>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A193" s="3" t="s">
+      <c r="A193" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B193" s="4"/>
+      <c r="B193" s="6"/>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
@@ -3852,28 +3880,28 @@
       <c r="B196" s="6"/>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A197" s="5" t="s">
+      <c r="A197" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B197" s="6"/>
+      <c r="B197" s="2"/>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B198" s="6"/>
+      <c r="B198" s="4"/>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A199" s="2" t="s">
+      <c r="A199" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B199" s="2"/>
+      <c r="B199" s="6"/>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A200" s="3" t="s">
+      <c r="A200" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B200" s="4"/>
+      <c r="B200" s="6"/>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
@@ -3906,10 +3934,10 @@
       <c r="B205" s="6"/>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A206" s="5" t="s">
+      <c r="A206" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B206" s="6"/>
+      <c r="B206" s="4"/>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
@@ -3918,10 +3946,10 @@
       <c r="B207" s="6"/>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A208" s="3" t="s">
+      <c r="A208" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B208" s="4"/>
+      <c r="B208" s="6"/>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
@@ -3936,13 +3964,13 @@
       <c r="B210" s="6"/>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A211" s="5" t="s">
+      <c r="A211" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B211" s="6"/>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A212" s="5" t="s">
+      <c r="A212" s="7" t="s">
         <v>211</v>
       </c>
       <c r="B212" s="6"/>
@@ -3960,7 +3988,7 @@
       <c r="B214" s="6"/>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A215" s="7" t="s">
+      <c r="A215" s="5" t="s">
         <v>214</v>
       </c>
       <c r="B215" s="6"/>
@@ -3972,7 +4000,7 @@
       <c r="B216" s="6"/>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A217" s="5" t="s">
+      <c r="A217" s="7" t="s">
         <v>216</v>
       </c>
       <c r="B217" s="6"/>
@@ -4014,22 +4042,22 @@
       <c r="B223" s="6"/>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A224" s="7" t="s">
+      <c r="A224" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B224" s="6"/>
+      <c r="B224" s="4"/>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A225" s="7" t="s">
+      <c r="A225" s="5" t="s">
         <v>224</v>
       </c>
       <c r="B225" s="6"/>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A226" s="3" t="s">
+      <c r="A226" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B226" s="4"/>
+      <c r="B226" s="6"/>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
@@ -4037,7 +4065,7 @@
       </c>
       <c r="B227" s="6"/>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>227</v>
       </c>
@@ -4049,7 +4077,7 @@
       </c>
       <c r="B229" s="6"/>
     </row>
-    <row r="230" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="5" t="s">
         <v>229</v>
       </c>
@@ -4062,10 +4090,10 @@
       <c r="B231" s="6"/>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A232" s="5" t="s">
+      <c r="A232" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B232" s="6"/>
+      <c r="B232" s="4"/>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
@@ -4074,10 +4102,10 @@
       <c r="B233" s="6"/>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A234" s="3" t="s">
+      <c r="A234" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B234" s="4"/>
+      <c r="B234" s="6"/>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
@@ -4116,10 +4144,10 @@
       <c r="B240" s="6"/>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A241" s="5" t="s">
+      <c r="A241" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B241" s="6"/>
+      <c r="B241" s="4"/>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
@@ -4128,10 +4156,10 @@
       <c r="B242" s="6"/>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A243" s="3" t="s">
+      <c r="A243" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B243" s="4"/>
+      <c r="B243" s="6"/>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="5" t="s">
@@ -4139,7 +4167,7 @@
       </c>
       <c r="B244" s="6"/>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
         <v>244</v>
       </c>
@@ -4151,7 +4179,7 @@
       </c>
       <c r="B246" s="6"/>
     </row>
-    <row r="247" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="5" t="s">
         <v>246</v>
       </c>
@@ -4170,28 +4198,28 @@
       <c r="B249" s="6"/>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A250" s="5" t="s">
+      <c r="A250" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B250" s="6"/>
+      <c r="B250" s="2"/>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A251" s="5" t="s">
+      <c r="A251" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B251" s="6"/>
+      <c r="B251" s="4"/>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A252" s="2" t="s">
+      <c r="A252" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B252" s="2"/>
+      <c r="B252" s="6"/>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A253" s="3" t="s">
+      <c r="A253" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B253" s="4"/>
+      <c r="B253" s="6"/>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="5" t="s">
@@ -4218,10 +4246,10 @@
       <c r="B257" s="6"/>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A258" s="5" t="s">
+      <c r="A258" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="6"/>
+      <c r="B258" s="4"/>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
@@ -4230,10 +4258,10 @@
       <c r="B259" s="6"/>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A260" s="3" t="s">
+      <c r="A260" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B260" s="4"/>
+      <c r="B260" s="6"/>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
@@ -4260,10 +4288,10 @@
       <c r="B264" s="6"/>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A265" s="5" t="s">
+      <c r="A265" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B265" s="6"/>
+      <c r="B265" s="4"/>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="5" t="s">
@@ -4272,10 +4300,10 @@
       <c r="B266" s="6"/>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A267" s="3" t="s">
+      <c r="A267" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B267" s="4"/>
+      <c r="B267" s="6"/>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
@@ -4289,7 +4317,7 @@
       </c>
       <c r="B269" s="6"/>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>269</v>
       </c>
@@ -4301,14 +4329,14 @@
       </c>
       <c r="B271" s="6"/>
     </row>
-    <row r="272" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A272" s="5" t="s">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272" s="7" t="s">
         <v>271</v>
       </c>
       <c r="B272" s="6"/>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A273" s="5" t="s">
+      <c r="A273" s="7" t="s">
         <v>272</v>
       </c>
       <c r="B273" s="6"/>
@@ -4332,22 +4360,22 @@
       <c r="B276" s="6"/>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A277" s="7" t="s">
+      <c r="A277" s="5" t="s">
         <v>276</v>
       </c>
       <c r="B277" s="6"/>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A278" s="7" t="s">
+      <c r="A278" s="5" t="s">
         <v>277</v>
       </c>
       <c r="B278" s="6"/>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A279" s="5" t="s">
+      <c r="A279" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B279" s="6"/>
+      <c r="B279" s="4"/>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
@@ -4356,10 +4384,10 @@
       <c r="B280" s="6"/>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A281" s="3" t="s">
+      <c r="A281" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B281" s="4"/>
+      <c r="B281" s="6"/>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
@@ -4380,10 +4408,10 @@
       <c r="B284" s="6"/>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A285" s="5" t="s">
+      <c r="A285" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B285" s="6"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="5" t="s">
@@ -4392,10 +4420,10 @@
       <c r="B286" s="6"/>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A287" s="3" t="s">
+      <c r="A287" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B287" s="4"/>
+      <c r="B287" s="6"/>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="5" t="s">
@@ -4428,40 +4456,40 @@
       <c r="B292" s="6"/>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A293" s="5" t="s">
+      <c r="A293" s="7" t="s">
         <v>292</v>
       </c>
       <c r="B293" s="6"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A294" s="5" t="s">
+    <row r="294" spans="1:2" ht="26" x14ac:dyDescent="0.35">
+      <c r="A294" s="7" t="s">
         <v>293</v>
       </c>
       <c r="B294" s="6"/>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A295" s="7" t="s">
+      <c r="A295" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B295" s="6"/>
-    </row>
-    <row r="296" spans="1:2" ht="26" x14ac:dyDescent="0.35">
-      <c r="A296" s="7" t="s">
+      <c r="B295" s="2"/>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B296" s="6"/>
+      <c r="B296" s="4"/>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A297" s="2" t="s">
+      <c r="A297" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B297" s="2"/>
+      <c r="B297" s="6"/>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A298" s="3" t="s">
+      <c r="A298" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B298" s="4"/>
+      <c r="B298" s="6"/>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="5" t="s">
@@ -4494,10 +4522,10 @@
       <c r="B303" s="6"/>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A304" s="5" t="s">
+      <c r="A304" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B304" s="6"/>
+      <c r="B304" s="4"/>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="5" t="s">
@@ -4506,10 +4534,10 @@
       <c r="B305" s="6"/>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A306" s="3" t="s">
+      <c r="A306" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B306" s="4"/>
+      <c r="B306" s="6"/>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="5" t="s">
@@ -4536,10 +4564,10 @@
       <c r="B310" s="6"/>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A311" s="5" t="s">
+      <c r="A311" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B311" s="6"/>
+      <c r="B311" s="4"/>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" s="5" t="s">
@@ -4548,10 +4576,10 @@
       <c r="B312" s="6"/>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A313" s="3" t="s">
+      <c r="A313" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B313" s="4"/>
+      <c r="B313" s="6"/>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" s="5" t="s">
@@ -4572,10 +4600,10 @@
       <c r="B316" s="6"/>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A317" s="5" t="s">
+      <c r="A317" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B317" s="6"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" s="5" t="s">
@@ -4584,10 +4612,10 @@
       <c r="B318" s="6"/>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A319" s="3" t="s">
+      <c r="A319" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B319" s="4"/>
+      <c r="B319" s="6"/>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" s="5" t="s">
@@ -4614,13 +4642,13 @@
       <c r="B323" s="6"/>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A324" s="5" t="s">
+      <c r="A324" s="7" t="s">
         <v>323</v>
       </c>
       <c r="B324" s="6"/>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A325" s="5" t="s">
+      <c r="A325" s="7" t="s">
         <v>324</v>
       </c>
       <c r="B325" s="6"/>
@@ -4644,13 +4672,13 @@
       <c r="B328" s="6"/>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A329" s="7" t="s">
+      <c r="A329" s="5" t="s">
         <v>328</v>
       </c>
       <c r="B329" s="6"/>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A330" s="7" t="s">
+      <c r="A330" s="5" t="s">
         <v>329</v>
       </c>
       <c r="B330" s="6"/>
@@ -4668,10 +4696,10 @@
       <c r="B332" s="6"/>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A333" s="5" t="s">
+      <c r="A333" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B333" s="6"/>
+      <c r="B333" s="4"/>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" s="5" t="s">
@@ -4680,10 +4708,10 @@
       <c r="B334" s="6"/>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A335" s="3" t="s">
+      <c r="A335" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B335" s="4"/>
+      <c r="B335" s="6"/>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" s="5" t="s">
@@ -4722,10 +4750,10 @@
       <c r="B341" s="6"/>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A342" s="5" t="s">
+      <c r="A342" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B342" s="6"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" s="5" t="s">
@@ -4734,10 +4762,10 @@
       <c r="B343" s="6"/>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A344" s="3" t="s">
+      <c r="A344" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B344" s="4"/>
+      <c r="B344" s="6"/>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" s="5" t="s">
@@ -4757,7 +4785,7 @@
       </c>
       <c r="B347" s="6"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A348" s="5" t="s">
         <v>347</v>
       </c>
@@ -4769,17 +4797,17 @@
       </c>
       <c r="B349" s="6"/>
     </row>
-    <row r="350" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" s="5" t="s">
         <v>349</v>
       </c>
       <c r="B350" s="6"/>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A351" s="5" t="s">
+      <c r="A351" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B351" s="6"/>
+      <c r="B351" s="4"/>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" s="5" t="s">
@@ -4788,10 +4816,10 @@
       <c r="B352" s="6"/>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A353" s="3" t="s">
+      <c r="A353" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B353" s="4"/>
+      <c r="B353" s="6"/>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" s="5" t="s">
@@ -4811,41 +4839,41 @@
       </c>
       <c r="B356" s="6"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A357" s="5" t="s">
         <v>356</v>
       </c>
       <c r="B357" s="6"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A358" s="5" t="s">
         <v>357</v>
       </c>
       <c r="B358" s="6"/>
     </row>
-    <row r="359" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A359" s="5" t="s">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A359" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B359" s="6"/>
-    </row>
-    <row r="360" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A360" s="5" t="s">
+      <c r="B359" s="2"/>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A360" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B360" s="6"/>
+      <c r="B360" s="4"/>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A361" s="2" t="s">
+      <c r="A361" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B361" s="2"/>
+      <c r="B361" s="6"/>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A362" s="3" t="s">
+      <c r="A362" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B362" s="4"/>
+      <c r="B362" s="6"/>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" s="5" t="s">
@@ -4890,10 +4918,10 @@
       <c r="B369" s="6"/>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A370" s="5" t="s">
+      <c r="A370" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B370" s="6"/>
+      <c r="B370" s="4"/>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" s="5" t="s">
@@ -4902,10 +4930,10 @@
       <c r="B371" s="6"/>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A372" s="3" t="s">
+      <c r="A372" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B372" s="4"/>
+      <c r="B372" s="6"/>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" s="5" t="s">
@@ -4955,7 +4983,7 @@
       </c>
       <c r="B380" s="6"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A381" s="5" t="s">
         <v>380</v>
       </c>
@@ -4967,14 +4995,14 @@
       </c>
       <c r="B382" s="6"/>
     </row>
-    <row r="383" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A383" s="5" t="s">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A383" s="7" t="s">
         <v>382</v>
       </c>
       <c r="B383" s="6"/>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A384" s="5" t="s">
+      <c r="A384" s="7" t="s">
         <v>383</v>
       </c>
       <c r="B384" s="6"/>
@@ -4998,13 +5026,13 @@
       <c r="B387" s="6"/>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A388" s="7" t="s">
+      <c r="A388" s="5" t="s">
         <v>387</v>
       </c>
       <c r="B388" s="6"/>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A389" s="7" t="s">
+    <row r="389" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+      <c r="A389" s="5" t="s">
         <v>388</v>
       </c>
       <c r="B389" s="6"/>
@@ -5015,23 +5043,23 @@
       </c>
       <c r="B390" s="6"/>
     </row>
-    <row r="391" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A391" s="5" t="s">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A391" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B391" s="6"/>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B391" s="4"/>
+    </row>
+    <row r="392" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A392" s="5" t="s">
         <v>391</v>
       </c>
       <c r="B392" s="6"/>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A393" s="3" t="s">
+      <c r="A393" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B393" s="4"/>
+      <c r="B393" s="6"/>
     </row>
     <row r="394" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A394" s="5" t="s">
@@ -5045,13 +5073,13 @@
       </c>
       <c r="B395" s="6"/>
     </row>
-    <row r="396" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" s="5" t="s">
         <v>395</v>
       </c>
       <c r="B396" s="6"/>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A397" s="5" t="s">
         <v>396</v>
       </c>
@@ -5074,18 +5102,6 @@
         <v>399</v>
       </c>
       <c r="B400" s="6"/>
-    </row>
-    <row r="401" spans="1:2" ht="28" x14ac:dyDescent="0.35">
-      <c r="A401" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="B401" s="6"/>
-    </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A402" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="B402" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5111,1285 +5127,1285 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B18" s="6"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B19" s="4"/>
     </row>
     <row r="20" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B24" s="6"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B25" s="6"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B27" s="6"/>
     </row>
     <row r="28" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B28" s="6"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B29" s="4"/>
     </row>
     <row r="30" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B35" s="6"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B36" s="4"/>
     </row>
     <row r="37" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B37" s="6"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B38" s="6"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B40" s="6"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B41" s="6"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B42" s="6"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B43" s="6"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B44" s="6"/>
     </row>
     <row r="45" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B46" s="6"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B49" s="6"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B50" s="6"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B53" s="6"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B54" s="6"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B55" s="6"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B56" s="6"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B57" s="4"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B58" s="6"/>
     </row>
     <row r="59" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B59" s="6"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B60" s="6"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B61" s="6"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B62" s="6"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B63" s="6"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B65" s="6"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B66" s="6"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B67" s="6"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B68" s="6"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B69" s="6"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B70" s="4"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B71" s="6"/>
     </row>
     <row r="72" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B72" s="6"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B73" s="6"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B74" s="6"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B75" s="6"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B76" s="6"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B77" s="6"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B78" s="6"/>
     </row>
     <row r="79" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B79" s="6"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B80" s="4"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B81" s="6"/>
     </row>
     <row r="82" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B82" s="6"/>
     </row>
     <row r="83" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B83" s="6"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B84" s="6"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B85" s="6"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B86" s="2"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B87" s="4"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B88" s="6"/>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B89" s="6"/>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B90" s="6"/>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B91" s="6"/>
     </row>
     <row r="92" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B92" s="6"/>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B93" s="6"/>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B95" s="6"/>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B96" s="6"/>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B97" s="6"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B98" s="6"/>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B99" s="6"/>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B100" s="6"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B101" s="4"/>
     </row>
     <row r="102" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B102" s="6"/>
     </row>
     <row r="103" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B103" s="6"/>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B104" s="6"/>
     </row>
     <row r="105" spans="1:2" ht="42" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B105" s="6"/>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B106" s="4"/>
     </row>
     <row r="107" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B107" s="6"/>
     </row>
     <row r="108" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B108" s="6"/>
     </row>
     <row r="109" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B109" s="6"/>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B110" s="6"/>
     </row>
     <row r="111" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B111" s="6"/>
     </row>
     <row r="112" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B112" s="6"/>
     </row>
     <row r="113" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B113" s="6"/>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B114" s="2"/>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B115" s="4"/>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B116" s="6"/>
     </row>
     <row r="117" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B117" s="6"/>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B118" s="6"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B119" s="6"/>
     </row>
     <row r="120" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B120" s="6"/>
     </row>
     <row r="121" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B121" s="6"/>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B122" s="6"/>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B123" s="4"/>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B124" s="6"/>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B125" s="6"/>
     </row>
     <row r="126" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B126" s="6"/>
     </row>
     <row r="127" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B127" s="6"/>
     </row>
     <row r="128" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B128" s="6"/>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B129" s="6"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B130" s="6"/>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B131" s="6"/>
     </row>
     <row r="132" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B132" s="6"/>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B133" s="4"/>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B134" s="6"/>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B135" s="6"/>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B136" s="6"/>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B137" s="6"/>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B138" s="2"/>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B139" s="4"/>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B140" s="6"/>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B141" s="6"/>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B142" s="6"/>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B143" s="6"/>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B144" s="6"/>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B145" s="6"/>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B146" s="6"/>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B147" s="6"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B148" s="6"/>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B149" s="6"/>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B150" s="6"/>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B151" s="6"/>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B152" s="6"/>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B153" s="6"/>
     </row>
     <row r="154" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B154" s="6"/>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B155" s="4"/>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B156" s="6"/>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B157" s="6"/>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B158" s="6"/>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B159" s="6"/>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B160" s="6"/>
     </row>
     <row r="161" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B161" s="6"/>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B162" s="6"/>
     </row>
     <row r="163" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B163" s="6"/>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B164" s="6"/>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B165" s="4"/>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B166" s="6"/>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B167" s="6"/>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B168" s="6"/>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B169" s="6"/>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B170" s="6"/>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B171" s="6"/>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B172" s="6"/>
     </row>
     <row r="173" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B173" s="6"/>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B174" s="4"/>
     </row>
     <row r="175" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B175" s="6"/>
     </row>
     <row r="176" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B176" s="6"/>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B177" s="6"/>
     </row>
     <row r="178" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B178" s="6"/>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B179" s="6"/>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B180" s="6"/>
     </row>
     <row r="181" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B181" s="6"/>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B182" s="2"/>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B183" s="4"/>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B184" s="6"/>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B185" s="6"/>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B186" s="6"/>
     </row>
     <row r="187" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B187" s="6"/>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B188" s="6"/>
     </row>
     <row r="189" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B189" s="6"/>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B190" s="6"/>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B191" s="4"/>
     </row>
     <row r="192" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B192" s="6"/>
     </row>
     <row r="193" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B193" s="6"/>
     </row>
     <row r="194" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B194" s="6"/>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B195" s="6"/>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B196" s="6"/>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B197" s="6"/>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B198" s="4"/>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B199" s="6"/>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B200" s="6"/>
     </row>
     <row r="201" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B201" s="6"/>
     </row>
     <row r="202" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B202" s="6"/>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B203" s="4"/>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B204" s="6"/>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B205" s="6"/>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B206" s="6"/>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B207" s="6"/>
     </row>
     <row r="208" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B208" s="6"/>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B209" s="4"/>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B210" s="6"/>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B211" s="6"/>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B212" s="6"/>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B213" s="6"/>
     </row>
     <row r="214" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A214" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B214" s="6"/>
     </row>
     <row r="215" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B215" s="6"/>
     </row>
@@ -6417,709 +6433,709 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B13" s="6"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B18" s="6"/>
     </row>
     <row r="19" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B19" s="6"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B24" s="6"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B25" s="6"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B27" s="6"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B28" s="4"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B29" s="6"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B34" s="4"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B35" s="6"/>
     </row>
     <row r="36" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B36" s="6"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B37" s="6"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B38" s="6"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B40" s="6"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B41" s="6"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B42" s="6"/>
     </row>
     <row r="43" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B43" s="6"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B44" s="6"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B45" s="4"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B46" s="6"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B48" s="6"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B49" s="6"/>
     </row>
     <row r="50" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B50" s="6"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B53" s="6"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B54" s="4"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B55" s="6"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B56" s="6"/>
     </row>
     <row r="57" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B57" s="6"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B58" s="6"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B60" s="6"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B61" s="6"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B62" s="6"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B63" s="6"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B65" s="6"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B66" s="6"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B67" s="6"/>
     </row>
     <row r="68" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B68" s="6"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B69" s="2"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B70" s="4"/>
     </row>
     <row r="71" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B71" s="6"/>
     </row>
     <row r="72" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B72" s="6"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B73" s="6"/>
     </row>
     <row r="74" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B74" s="6"/>
     </row>
     <row r="75" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B75" s="6"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B76" s="4"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B77" s="6"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B78" s="6"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B79" s="6"/>
     </row>
     <row r="80" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B80" s="6"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B81" s="6"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B82" s="6"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B83" s="6"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B84" s="6"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B85" s="6"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B86" s="6"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B87" s="6"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B88" s="6"/>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B89" s="4"/>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B90" s="6"/>
     </row>
     <row r="91" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B91" s="6"/>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B92" s="6"/>
     </row>
     <row r="93" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B93" s="6"/>
     </row>
     <row r="94" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B94" s="6"/>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B95" s="6"/>
     </row>
     <row r="96" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B96" s="6"/>
     </row>
     <row r="97" spans="1:2" ht="26" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B97" s="6"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B98" s="6"/>
     </row>
     <row r="99" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B99" s="6"/>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B100" s="2"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B101" s="4"/>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B102" s="6"/>
     </row>
     <row r="103" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B103" s="6"/>
     </row>
     <row r="104" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B104" s="6"/>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B105" s="6"/>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B106" s="6"/>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B107" s="6"/>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B108" s="6"/>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B109" s="6"/>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B110" s="4"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B111" s="6"/>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B112" s="6"/>
     </row>
     <row r="113" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B113" s="6"/>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B114" s="4"/>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B115" s="6"/>
     </row>
     <row r="116" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B116" s="6"/>
     </row>
     <row r="117" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B117" s="6"/>
     </row>
     <row r="118" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B118" s="6"/>
     </row>
     <row r="119" spans="1:2" ht="28" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B119" s="6"/>
     </row>
